--- a/data/trending_integrated_20261016_14.xlsx
+++ b/data/trending_integrated_20261016_14.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8100</v>
+        <v>8940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.29%</t>
+          <t>'+25.03%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.26</v>
+        <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G2" t="n">
-        <v>240</v>
+        <v>343</v>
       </c>
       <c r="H2" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6570</v>
+        <v>7150</v>
       </c>
       <c r="K2" t="n">
-        <v>6850</v>
+        <v>7430</v>
       </c>
       <c r="L2" t="n">
-        <v>8540</v>
+        <v>8980</v>
       </c>
       <c r="M2" t="n">
-        <v>6630</v>
+        <v>7300</v>
       </c>
       <c r="N2" t="n">
-        <v>0.99</v>
+        <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>78722946735</v>
+        <v>218101396500</v>
       </c>
       <c r="P2" t="n">
-        <v>10300</v>
+        <v>8980</v>
       </c>
       <c r="Q2" t="n">
-        <v>952</v>
+        <v>2270</v>
       </c>
       <c r="R2" t="n">
-        <v>-9000</v>
+        <v>36000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>매수세 유입 및 신고가 돌파 기대. 단기 급등 후 차익 실현 및 급락 주의.</t>
+          <t>최근의 폭락장 속에서도 인수합병 기대감과 함께 긍정적인 가격 상승 전망이 제시됩니다. 특히 HT로보틱스의 코스닥 편입 가능성과 텐버거 가능성이 언급됩니다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신고가', '매집', '급등']</t>
+          <t>['인수합병', 'HT로보틱스', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8810</v>
+        <v>7970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.22%</t>
+          <t>'+21.31%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.12</v>
+        <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>184</v>
+        <v>125</v>
       </c>
       <c r="F3" t="n">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>330</v>
+        <v>233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7150</v>
+        <v>6570</v>
       </c>
       <c r="K3" t="n">
-        <v>7430</v>
+        <v>6850</v>
       </c>
       <c r="L3" t="n">
-        <v>8970</v>
+        <v>8540</v>
       </c>
       <c r="M3" t="n">
-        <v>7300</v>
+        <v>6630</v>
       </c>
       <c r="N3" t="n">
-        <v>1.84</v>
+        <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>212646499215</v>
+        <v>79480425400</v>
       </c>
       <c r="P3" t="n">
-        <v>8970</v>
+        <v>10300</v>
       </c>
       <c r="Q3" t="n">
-        <v>2270</v>
+        <v>952</v>
       </c>
       <c r="R3" t="n">
-        <v>36000</v>
+        <v>-9000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>폭락장 속에서도 견조한 흐름. 인수합병 기대감 및 4년 묵은 물량 소화. 일부 단타 이익 실현.</t>
+          <t>군 공항 이전 관련 정치적 이슈와 함께 긍정적인 신고가 및 8만원 돌파 가능성이 제기됩니다. 일부에서는 정치인들의 행보에 대한 우려를 표하며, 호남 반도체 관련주 상승을 언급합니다.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['인수합병', '물량 소화', '단타']</t>
+          <t>['군공항 이전', '정치', '호남반도체']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8340</v>
+        <v>8250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.64%</t>
+          <t>'+15.38%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>52645525760</v>
+        <v>53129932530</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9670</v>
+        <v>9560</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.39%</t>
+          <t>'+8.14%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>90624125810</v>
+        <v>91350097220</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>222000</v>
+        <v>10450</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.71%</t>
+          <t>'+5.24%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>488</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>1237</v>
+        <v>149</v>
       </c>
       <c r="H6" t="n">
-        <v>45.98</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>210000</v>
+        <v>9930</v>
       </c>
       <c r="K6" t="n">
-        <v>215000</v>
+        <v>10100</v>
       </c>
       <c r="L6" t="n">
-        <v>222500</v>
+        <v>11100</v>
       </c>
       <c r="M6" t="n">
-        <v>210500</v>
+        <v>9860</v>
       </c>
       <c r="N6" t="n">
-        <v>46.16</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2849732817250</v>
+        <v>32837060145</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>3200</v>
       </c>
       <c r="R6" t="n">
-        <v>-231000</v>
+        <v>-121000</v>
       </c>
       <c r="S6" t="n">
-        <v>-192000</v>
+        <v>-8000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 요인 및 직원 성과급 지급 반대 논란 속에 외국인 이탈 지속. 다만, 단기 반등 기대감 존재.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인 이탈', '성과급', '반등 기대']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10480</v>
+        <v>220250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.54%</t>
+          <t>'+4.88%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>488</v>
       </c>
       <c r="G7" t="n">
-        <v>149</v>
+        <v>1257</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>45.98</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,143 +1055,143 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9930</v>
+        <v>210000</v>
       </c>
       <c r="K7" t="n">
-        <v>10100</v>
+        <v>215000</v>
       </c>
       <c r="L7" t="n">
-        <v>11100</v>
+        <v>222500</v>
       </c>
       <c r="M7" t="n">
-        <v>9860</v>
+        <v>210500</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>32567827645</v>
+        <v>2952148996250</v>
       </c>
       <c r="P7" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3200</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-121000</v>
+        <v>-231000</v>
       </c>
       <c r="S7" t="n">
-        <v>-8000</v>
+        <v>-192000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>정치적 이슈와 직원 상여금 지급 부결 요구가 혼재된 가운데, 외인 이탈 우려 및 기술적 지표 하락 전망이 제기됩니다. 일부 긍정적 가격 전망도 존재합니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['이재명', '외국인', '기술적 지표']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15750</v>
+        <v>66000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.42%</t>
+          <t>'+4.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>227</v>
+        <v>150</v>
       </c>
       <c r="F8" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G8" t="n">
-        <v>239</v>
+        <v>496</v>
       </c>
       <c r="H8" t="n">
-        <v>0.11</v>
+        <v>22.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14940</v>
+        <v>63300</v>
       </c>
       <c r="K8" t="n">
-        <v>14940</v>
+        <v>63900</v>
       </c>
       <c r="L8" t="n">
-        <v>16350</v>
+        <v>66400</v>
       </c>
       <c r="M8" t="n">
-        <v>14330</v>
+        <v>63500</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>22.11</v>
       </c>
       <c r="O8" t="n">
-        <v>67814258250</v>
+        <v>110139317550</v>
       </c>
       <c r="P8" t="n">
-        <v>30800</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>9810</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>6000</v>
+        <v>78000</v>
       </c>
       <c r="S8" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>상장 사기 논란 및 지나치게 높은 공모가 지적. 경영진 사퇴 요구와 함께 자진 상폐 주장 제기.</t>
+          <t>뉴스케일파워 상승 등 긍정적인 뉴스 플로우와 함께 주가 상승에 대한 기대감이 존재합니다. 그러나 일부에서는 경영진의 주주 환원 정책 부재와 신뢰도 문제를 지적하며 신중한 태도를 보입니다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['상장 사기', '공모가', '자진 상폐']</t>
+          <t>['뉴스케일파워', '주주 환원', '신뢰도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1322000</v>
+        <v>1312000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.75%</t>
+          <t>'+3.96%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="G9" t="n">
-        <v>1285</v>
+        <v>1270</v>
       </c>
       <c r="H9" t="n">
         <v>48.85</v>
@@ -1245,7 +1245,7 @@
         <v>1290000</v>
       </c>
       <c r="L9" t="n">
-        <v>1324000</v>
+        <v>1325000</v>
       </c>
       <c r="M9" t="n">
         <v>1247000</v>
@@ -1254,7 +1254,7 @@
         <v>49.02</v>
       </c>
       <c r="O9" t="n">
-        <v>4149214584000</v>
+        <v>4279620130000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 요인과 외인 매도에 대한 강한 불만 표출. 주가 하락에 대한 비판과 함께 일부 기대감 존재.</t>
+          <t>주가 하락에 대한 불만이 고조되며 정부 및 경영진에 대한 비판이 제기됩니다. 솔리다임 상장 이슈와 외국인 매매 동향이 주가 하락 원인으로 분석되며, 일부 투자자들은 긍정적인 장기 전망을 제시합니다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가관리', '외국인', '폭락']</t>
+          <t>['주가 관리', '솔리다임', '외국인']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66200</v>
+        <v>42300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.58%</t>
+          <t>'+3.80%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>149</v>
+        <v>281</v>
       </c>
       <c r="F10" t="n">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="G10" t="n">
-        <v>481</v>
+        <v>1154</v>
       </c>
       <c r="H10" t="n">
-        <v>22.1</v>
+        <v>12.97</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>63300</v>
+        <v>40750</v>
       </c>
       <c r="K10" t="n">
-        <v>63900</v>
+        <v>40600</v>
       </c>
       <c r="L10" t="n">
-        <v>66300</v>
+        <v>42500</v>
       </c>
       <c r="M10" t="n">
-        <v>63500</v>
+        <v>40050</v>
       </c>
       <c r="N10" t="n">
-        <v>22.11</v>
+        <v>12.84</v>
       </c>
       <c r="O10" t="n">
-        <v>106941991850</v>
+        <v>15722808275</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>78000</v>
+        <v>62000</v>
       </c>
       <c r="S10" t="n">
-        <v>11000</v>
+        <v>-5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>뉴스케일파워 등 원전주 상승세. 스페이스X 선정 및 주주환원 정책 요구.</t>
+          <t>담관암 FDA 승인 가능성 및 CLASS1 발표에 대한 기대감이 높게 형성되어 있습니다. 긍정적인 야간 선물 흐름과 함께 임상 결과에 대한 강한 확신을 보이며, 일부는 진양곤 회장에 대한 언급도 합니다.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전주', '뉴스케일파워', '주주환원']</t>
+          <t>['FDA 승인', 'CLASS1', '담관암']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42450</v>
+        <v>15450</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.17%</t>
+          <t>'+3.41%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>277</v>
+        <v>236</v>
       </c>
       <c r="F11" t="n">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="G11" t="n">
-        <v>1129</v>
+        <v>244</v>
       </c>
       <c r="H11" t="n">
-        <v>12.97</v>
+        <v>0.11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>40750</v>
+        <v>14940</v>
       </c>
       <c r="K11" t="n">
-        <v>40600</v>
+        <v>14940</v>
       </c>
       <c r="L11" t="n">
-        <v>42500</v>
+        <v>16350</v>
       </c>
       <c r="M11" t="n">
-        <v>40050</v>
+        <v>14330</v>
       </c>
       <c r="N11" t="n">
-        <v>12.84</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>15327755050</v>
+        <v>70169798515</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>30800</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>9810</v>
       </c>
       <c r="R11" t="n">
-        <v>62000</v>
+        <v>6000</v>
       </c>
       <c r="S11" t="n">
-        <v>-5000</v>
+        <v>2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 기대감 속, 클래스 1 발표 가능성 및 임상 결과에 대한 논의. 과거 사례 언급하며 신중론도 제기.</t>
+          <t>상장 사기 및 경영진의 무능함을 지적하며 주가 조작 의혹이 제기됩니다. 공모가 대비 고평가 논란과 함께 자진 상폐 요구가 나오고 있으며, 금감원 조사를 촉구하는 의견도 있습니다.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['FDA', '임상', '승인']</t>
+          <t>['상장 사기', '경영진', '공모가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18850</v>
+        <v>18790</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.74%</t>
+          <t>'+3.41%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H12" t="n">
         <v>27.77</v>
@@ -1530,7 +1530,7 @@
         <v>27.82</v>
       </c>
       <c r="O12" t="n">
-        <v>43549022035</v>
+        <v>45316478085</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13450</v>
+        <v>13470</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H13" t="n">
         <v>3.42</v>
@@ -1622,7 +1622,7 @@
         <v>3.21</v>
       </c>
       <c r="O13" t="n">
-        <v>44313546535</v>
+        <v>45082654415</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15070</v>
+        <v>15050</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+2.59%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="H14" t="n">
         <v>9.779999999999999</v>
@@ -1714,7 +1714,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>32433073685</v>
+        <v>32966038665</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17920</v>
+        <v>17850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.58%</t>
+          <t>'+2.18%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G15" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>159713557035</v>
+        <v>161097482410</v>
       </c>
       <c r="P15" t="n">
         <v>28800</v>
@@ -1872,7 +1872,7 @@
         <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="H16" t="n">
         <v>9.23</v>
@@ -1898,7 +1898,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>42347039675</v>
+        <v>43154807475</v>
       </c>
       <c r="P16" t="n">
         <v>24950</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20500</v>
+        <v>20550</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.20%</t>
+          <t>'-0.96%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G17" t="n">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="H17" t="n">
         <v>4.28</v>
@@ -1990,7 +1990,7 @@
         <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>71001972520</v>
+        <v>72132760420</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26700</v>
+        <v>26750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.34%</t>
+          <t>'-9.17%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F18" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G18" t="n">
-        <v>620</v>
+        <v>645</v>
       </c>
       <c r="H18" t="n">
-        <v>53.32</v>
+        <v>53.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>159091897700</v>
+        <v>164286886600</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 급락. 외국인 및 기관 매도세 집중되며 추가 하락 전망. 유튜버 발언 신뢰도 하락.</t>
+          <t>실적 발표 후 배당 관련 언급이 있으나, 전반적으로 외인 및 기관의 대규모 매도와 함께 급락이 예상되는 부정적인 의견이 지배적입니다. 일부는 저점 매수 기회를 언급합니다.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적 발표', '외국인 매도', '추가 하락']</t>
+          <t>['실적 발표', '외국인 매도', '급락']</t>
         </is>
       </c>
       <c r="X18" t="n">

--- a/data/trending_integrated_20261016_14.xlsx
+++ b/data/trending_integrated_20261016_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8940</v>
+        <v>9100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+25.03%</t>
+          <t>'+27.27%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F2" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G2" t="n">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -601,7 +601,7 @@
         <v>7430</v>
       </c>
       <c r="L2" t="n">
-        <v>8980</v>
+        <v>9180</v>
       </c>
       <c r="M2" t="n">
         <v>7300</v>
@@ -610,32 +610,32 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>218101396500</v>
+        <v>228411516300</v>
       </c>
       <c r="P2" t="n">
-        <v>8980</v>
+        <v>9180</v>
       </c>
       <c r="Q2" t="n">
         <v>2270</v>
       </c>
       <c r="R2" t="n">
-        <v>36000</v>
+        <v>122000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>최근의 폭락장 속에서도 인수합병 기대감과 함께 긍정적인 가격 상승 전망이 제시됩니다. 특히 HT로보틱스의 코스닥 편입 가능성과 텐버거 가능성이 언급됩니다.</t>
+          <t>인수합병 가능성과 함께 4년 묵은 물량 해소에 대한 기대감이 언급됩니다. 일부에서는 거래량 증가 및 급락에 대한 의견도 있습니다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', 'HT로보틱스', '텐버거']</t>
+          <t>['인수합병', '물량', '거래량']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7970</v>
+        <v>8020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.31%</t>
+          <t>'+22.07%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>79480425400</v>
+        <v>80229045640</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -711,7 +711,7 @@
         <v>952</v>
       </c>
       <c r="R3" t="n">
-        <v>-9000</v>
+        <v>-8000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8250</v>
+        <v>8270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.38%</t>
+          <t>'+15.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>53129932530</v>
+        <v>53448321255</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -803,7 +803,7 @@
         <v>1206</v>
       </c>
       <c r="R4" t="n">
-        <v>231000</v>
+        <v>229000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9560</v>
+        <v>9545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.14%</t>
+          <t>'+7.98%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>91350097220</v>
+        <v>91895118575</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -895,7 +895,7 @@
         <v>465</v>
       </c>
       <c r="R5" t="n">
-        <v>-157000</v>
+        <v>-153000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10450</v>
+        <v>10420</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.24%</t>
+          <t>'+4.93%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>32837060145</v>
+        <v>33042673755</v>
       </c>
       <c r="P6" t="n">
         <v>19380</v>
@@ -987,10 +987,10 @@
         <v>3200</v>
       </c>
       <c r="R6" t="n">
-        <v>-121000</v>
+        <v>-128000</v>
       </c>
       <c r="S6" t="n">
-        <v>-8000</v>
+        <v>-10000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220250</v>
+        <v>15630</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.88%</t>
+          <t>'+4.62%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>242</v>
       </c>
       <c r="F7" t="n">
-        <v>488</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
-        <v>1257</v>
+        <v>246</v>
       </c>
       <c r="H7" t="n">
-        <v>45.98</v>
+        <v>0.11</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>210000</v>
+        <v>14940</v>
       </c>
       <c r="K7" t="n">
-        <v>215000</v>
+        <v>14940</v>
       </c>
       <c r="L7" t="n">
-        <v>222500</v>
+        <v>16350</v>
       </c>
       <c r="M7" t="n">
-        <v>210500</v>
+        <v>14330</v>
       </c>
       <c r="N7" t="n">
-        <v>46.16</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2952148996250</v>
+        <v>72731376005</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>30800</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>9810</v>
       </c>
       <c r="R7" t="n">
-        <v>-231000</v>
+        <v>-2000</v>
       </c>
       <c r="S7" t="n">
-        <v>-192000</v>
+        <v>3000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 직원 상여금 지급 부결 요구가 혼재된 가운데, 외인 이탈 우려 및 기술적 지표 하락 전망이 제기됩니다. 일부 긍정적 가격 전망도 존재합니다.</t>
+          <t>상장 사기 의혹과 경영진 사퇴 요구가 제기되며, 공모가 대비 높은 가격에 대한 비판이 있습니다. 회사에 직접 전화하자는 의견도 있습니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['이재명', '외국인', '기술적 지표']</t>
+          <t>['상장사기', '공모가', '경영진']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66000</v>
+        <v>66200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.27%</t>
+          <t>'+4.58%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F8" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="H8" t="n">
         <v>22.1</v>
@@ -1162,7 +1162,7 @@
         <v>22.11</v>
       </c>
       <c r="O8" t="n">
-        <v>110139317550</v>
+        <v>113200854750</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1171,23 +1171,23 @@
         <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>78000</v>
+        <v>85000</v>
       </c>
       <c r="S8" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>뉴스케일파워 상승 등 긍정적인 뉴스 플로우와 함께 주가 상승에 대한 기대감이 존재합니다. 그러나 일부에서는 경영진의 주주 환원 정책 부재와 신뢰도 문제를 지적하며 신중한 태도를 보입니다.</t>
+          <t>뉴스케일파워와의 연관성 및 스페이스X 선택에 대한 언급이 있으며, 주주 환원 정책에 대한 요구가 있습니다. 일부에서는 긍정적인 주가 흐름을 기대합니다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '주주 환원', '신뢰도']</t>
+          <t>['뉴스케일파워', '주주환원', '원전']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1312000</v>
+        <v>219000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.96%</t>
+          <t>'+4.29%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="E9" t="n">
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G9" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="H9" t="n">
-        <v>48.85</v>
+        <v>45.98</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1262000</v>
+        <v>210000</v>
       </c>
       <c r="K9" t="n">
-        <v>1290000</v>
+        <v>215000</v>
       </c>
       <c r="L9" t="n">
-        <v>1325000</v>
+        <v>222500</v>
       </c>
       <c r="M9" t="n">
-        <v>1247000</v>
+        <v>210500</v>
       </c>
       <c r="N9" t="n">
-        <v>49.02</v>
+        <v>46.16</v>
       </c>
       <c r="O9" t="n">
-        <v>4279620130000</v>
+        <v>3041413965250</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>420500</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-545000</v>
+        <v>230000</v>
       </c>
       <c r="S9" t="n">
-        <v>-104000</v>
+        <v>-235000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 불만이 고조되며 정부 및 경영진에 대한 비판이 제기됩니다. 솔리다임 상장 이슈와 외국인 매매 동향이 주가 하락 원인으로 분석되며, 일부 투자자들은 긍정적인 장기 전망을 제시합니다.</t>
+          <t>직원 상여금 지급 반대 주장과 함께 정부 정책 및 외인 이탈에 대한 부정적 언급이 존재합니다. 일부에서는 상승 가능성을 제기합니다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가 관리', '솔리다임', '외국인']</t>
+          <t>['이평선', '저항선', '외인']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42300</v>
+        <v>42350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.80%</t>
+          <t>'+3.93%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F10" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G10" t="n">
-        <v>1154</v>
+        <v>1173</v>
       </c>
       <c r="H10" t="n">
         <v>12.97</v>
@@ -1346,7 +1346,7 @@
         <v>12.84</v>
       </c>
       <c r="O10" t="n">
-        <v>15722808275</v>
+        <v>15952817975</v>
       </c>
       <c r="P10" t="n">
         <v>69200</v>
@@ -1355,23 +1355,23 @@
         <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>62000</v>
+        <v>73000</v>
       </c>
       <c r="S10" t="n">
-        <v>-5000</v>
+        <v>-8000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 가능성 및 CLASS1 발표에 대한 기대감이 높게 형성되어 있습니다. 긍정적인 야간 선물 흐름과 함께 임상 결과에 대한 강한 확신을 보이며, 일부는 진양곤 회장에 대한 언급도 합니다.</t>
+          <t>CLASS1 발표 및 FDA 승인에 대한 기대감이 높은 가운데, 과거 사례와 비교하며 신중론을 제기하는 의견도 있습니다. 야간 선물 급등에 대한 언급도 있습니다.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FDA 승인', 'CLASS1', '담관암']</t>
+          <t>['CLASS1', 'FDA승인', '담관암']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,162 +1391,162 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15450</v>
+        <v>18810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.41%</t>
+          <t>'+3.52%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>236</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>244</v>
+        <v>179</v>
       </c>
       <c r="H11" t="n">
-        <v>0.11</v>
+        <v>27.77</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14940</v>
+        <v>18170</v>
       </c>
       <c r="K11" t="n">
-        <v>14940</v>
+        <v>18340</v>
       </c>
       <c r="L11" t="n">
-        <v>16350</v>
+        <v>18990</v>
       </c>
       <c r="M11" t="n">
-        <v>14330</v>
+        <v>18110</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>27.82</v>
       </c>
       <c r="O11" t="n">
-        <v>70169798515</v>
+        <v>46658436260</v>
       </c>
       <c r="P11" t="n">
-        <v>30800</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>9810</v>
+        <v>17210</v>
       </c>
       <c r="R11" t="n">
-        <v>6000</v>
+        <v>518000</v>
       </c>
       <c r="S11" t="n">
-        <v>2000</v>
+        <v>172000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>상장 사기 및 경영진의 무능함을 지적하며 주가 조작 의혹이 제기됩니다. 공모가 대비 고평가 논란과 함께 자진 상폐 요구가 나오고 있으며, 금감원 조사를 촉구하는 의견도 있습니다.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['상장 사기', '경영진', '공모가']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18790</v>
+        <v>13470</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.41%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.05</v>
+        <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>179</v>
+        <v>255</v>
       </c>
       <c r="H12" t="n">
-        <v>27.77</v>
+        <v>3.42</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18170</v>
+        <v>13060</v>
       </c>
       <c r="K12" t="n">
-        <v>18340</v>
+        <v>13390</v>
       </c>
       <c r="L12" t="n">
-        <v>18990</v>
+        <v>13620</v>
       </c>
       <c r="M12" t="n">
-        <v>18110</v>
+        <v>12910</v>
       </c>
       <c r="N12" t="n">
-        <v>27.82</v>
+        <v>3.21</v>
       </c>
       <c r="O12" t="n">
-        <v>45316478085</v>
+        <v>45563195580</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>17210</v>
+        <v>1640</v>
       </c>
       <c r="R12" t="n">
-        <v>311000</v>
+        <v>-102000</v>
       </c>
       <c r="S12" t="n">
-        <v>156000</v>
+        <v>-10000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,86 +1568,86 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13470</v>
+        <v>1301000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+3.09%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>476</v>
       </c>
       <c r="G13" t="n">
-        <v>241</v>
+        <v>1301</v>
       </c>
       <c r="H13" t="n">
-        <v>3.42</v>
+        <v>48.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13060</v>
+        <v>1262000</v>
       </c>
       <c r="K13" t="n">
-        <v>13390</v>
+        <v>1290000</v>
       </c>
       <c r="L13" t="n">
-        <v>13620</v>
+        <v>1325000</v>
       </c>
       <c r="M13" t="n">
-        <v>12910</v>
+        <v>1247000</v>
       </c>
       <c r="N13" t="n">
-        <v>3.21</v>
+        <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>45082654415</v>
+        <v>4398767424000</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>1640</v>
+        <v>420500</v>
       </c>
       <c r="R13" t="n">
-        <v>-119000</v>
+        <v>-543000</v>
       </c>
       <c r="S13" t="n">
-        <v>-11000</v>
+        <v>-39000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>주가 하락에 대한 경영진 비판과 함께 정부 정책 및 외인 자금 이탈에 대한 부정적인 인식이 강하게 나타납니다. 솔리다임 관련 이슈도 언급됩니다.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['주가관리', '외인', '솔리다임']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15050</v>
+        <v>15040</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.59%</t>
+          <t>'+2.52%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>489</v>
+        <v>522</v>
       </c>
       <c r="H14" t="n">
         <v>9.779999999999999</v>
@@ -1714,7 +1714,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>32966038665</v>
+        <v>33714134060</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1723,14 +1723,14 @@
         <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-130000</v>
+        <v>-134000</v>
       </c>
       <c r="S14" t="n">
-        <v>-47000</v>
+        <v>-61000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.43조원 규모 공급계약 체결 등 긍정적 공시 다수 확인. 주가 조작 의혹 제기 속에서도 실적 기반 상승 기대.</t>
+          <t>대규모 공급 계약 체결 공시가 있었으며, 주가 조작 의혹 및 금융 당국의 사모펀드 점검에 대한 언급이 있습니다. 긍정적인 전망을 제시하는 의견도 존재합니다.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공급 계약', '실적', '주가 조작 의혹']</t>
+          <t>['공급계약', '공시', '주가조작']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,70 +1759,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17850</v>
+        <v>23700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.18%</t>
+          <t>'+2.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>181</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>379</v>
+        <v>450</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>9.23</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17470</v>
+        <v>23200</v>
       </c>
       <c r="K15" t="n">
-        <v>18710</v>
+        <v>23250</v>
       </c>
       <c r="L15" t="n">
-        <v>20300</v>
+        <v>24250</v>
       </c>
       <c r="M15" t="n">
-        <v>17630</v>
+        <v>22900</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>161097482410</v>
+        <v>43909485750</v>
       </c>
       <c r="P15" t="n">
-        <v>28800</v>
+        <v>24950</v>
       </c>
       <c r="Q15" t="n">
-        <v>15780</v>
+        <v>17910</v>
       </c>
       <c r="R15" t="n">
-        <v>4000</v>
+        <v>635000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 상승 및 하락에 대한 상반된 전망. 반도체 테마 내에서의 저평가 논의 및 수급 불안정성 언급.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['저평가', '수급', '반도체']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,82 +1839,82 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23650</v>
+        <v>17550</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.94%</t>
+          <t>'+0.46%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="G16" t="n">
-        <v>441</v>
+        <v>386</v>
       </c>
       <c r="H16" t="n">
-        <v>9.23</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>23200</v>
+        <v>17470</v>
       </c>
       <c r="K16" t="n">
-        <v>23250</v>
+        <v>18710</v>
       </c>
       <c r="L16" t="n">
-        <v>24250</v>
+        <v>20300</v>
       </c>
       <c r="M16" t="n">
-        <v>22900</v>
+        <v>17250</v>
       </c>
       <c r="N16" t="n">
-        <v>9.210000000000001</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>43154807475</v>
+        <v>163879307415</v>
       </c>
       <c r="P16" t="n">
-        <v>24950</v>
+        <v>28800</v>
       </c>
       <c r="Q16" t="n">
-        <v>17910</v>
+        <v>15780</v>
       </c>
       <c r="R16" t="n">
-        <v>565000</v>
+        <v>4000</v>
       </c>
       <c r="S16" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>주가 상승 및 하락에 대한 상반된 전망. 반도체 테마 내에서의 저평가 논의 및 수급 불안정성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['저평가', '수급', '반도체']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20550</v>
+        <v>20650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.96%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F17" t="n">
         <v>77</v>
       </c>
       <c r="G17" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H17" t="n">
         <v>4.28</v>
@@ -1990,7 +1990,7 @@
         <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>72132760420</v>
+        <v>72574300845</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -1999,23 +1999,23 @@
         <v>6320</v>
       </c>
       <c r="R17" t="n">
-        <v>-63000</v>
+        <v>-49000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>양자보안 관련 긍정적 뉴스 및 신규 납품 요청. 보안 투자 확대 및 해킹 시도 증가.</t>
+          <t>농협, KDB 등으로부터 신규 납품 요청 및 러브콜이 쇄도한다는 뉴스와 함께 금융권 보안 투자 확대 소식이 있습니다. 양자보안 관련 긍정적 전망이 제시됩니다.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자보안', '납품', '보안 투자']</t>
+          <t>['양자보안', '보안투자', '납품요청']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26750</v>
+        <v>26775</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.17%</t>
+          <t>'-9.08%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F18" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G18" t="n">
-        <v>645</v>
+        <v>675</v>
       </c>
       <c r="H18" t="n">
         <v>53.3</v>
@@ -2082,7 +2082,7 @@
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>164286886600</v>
+        <v>168232366575</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2091,23 +2091,23 @@
         <v>21000</v>
       </c>
       <c r="R18" t="n">
-        <v>-408000</v>
+        <v>-456000</v>
       </c>
       <c r="S18" t="n">
-        <v>-244000</v>
+        <v>-315000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 배당 관련 언급이 있으나, 전반적으로 외인 및 기관의 대규모 매도와 함께 급락이 예상되는 부정적인 의견이 지배적입니다. 일부는 저점 매수 기회를 언급합니다.</t>
+          <t>실적 발표 후 급락 및 외인/기관의 대규모 매도에 대한 불만과 하락 추세에 대한 경고가 주를 이룹니다. 신한 증권에 대한 비판도 나타납니다.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적 발표', '외국인 매도', '급락']</t>
+          <t>['실적발표', '외인', '매도']</t>
         </is>
       </c>
       <c r="X18" t="n">

--- a/data/trending_integrated_20261016_14.xlsx
+++ b/data/trending_integrated_20261016_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9100</v>
+        <v>9080</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+27.27%</t>
+          <t>'+26.99%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="F2" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G2" t="n">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>228411516300</v>
+        <v>235439017330</v>
       </c>
       <c r="P2" t="n">
         <v>9180</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 가능성과 함께 4년 묵은 물량 해소에 대한 기대감이 언급됩니다. 일부에서는 거래량 증가 및 급락에 대한 의견도 있습니다.</t>
+          <t>장기 보유 물량 일부 매도 관찰. 인수합병 기대감 및 2차전지 섹터 편입 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '물량', '거래량']</t>
+          <t>['인수합병', '2차전지', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8020</v>
+        <v>7930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.07%</t>
+          <t>'+20.70%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>80229045640</v>
+        <v>80687584105</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군 공항 이전 관련 정치적 이슈와 함께 긍정적인 신고가 및 8만원 돌파 가능성이 제기됩니다. 일부에서는 정치인들의 행보에 대한 우려를 표하며, 호남 반도체 관련주 상승을 언급합니다.</t>
+          <t>군 공항 이전 관련 정치적 이슈와 함께 주가 급등 및 하락 혼재. 투경 종목으로 변동성 확대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군공항 이전', '정치', '호남반도체']</t>
+          <t>['군 공항 이전', '투경', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8270</v>
+        <v>8180</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.66%</t>
+          <t>'+14.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>53448321255</v>
+        <v>53978403205</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9545</v>
+        <v>9530</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.98%</t>
+          <t>'+7.81%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>91895118575</v>
+        <v>92452849540</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10420</v>
+        <v>10390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.93%</t>
+          <t>'+4.63%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>33042673755</v>
+        <v>33214724715</v>
       </c>
       <c r="P6" t="n">
         <v>19380</v>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15630</v>
+        <v>15590</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.62%</t>
+          <t>'+4.35%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G7" t="n">
         <v>246</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>72731376005</v>
+        <v>73781750980</v>
       </c>
       <c r="P7" t="n">
         <v>30800</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66200</v>
+        <v>218500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.58%</t>
+          <t>'+4.05%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="E8" t="n">
-        <v>151</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>484</v>
       </c>
       <c r="G8" t="n">
-        <v>522</v>
+        <v>1309</v>
       </c>
       <c r="H8" t="n">
-        <v>22.1</v>
+        <v>45.98</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>63300</v>
+        <v>210000</v>
       </c>
       <c r="K8" t="n">
-        <v>63900</v>
+        <v>215000</v>
       </c>
       <c r="L8" t="n">
-        <v>66400</v>
+        <v>222500</v>
       </c>
       <c r="M8" t="n">
-        <v>63500</v>
+        <v>210500</v>
       </c>
       <c r="N8" t="n">
-        <v>22.11</v>
+        <v>46.16</v>
       </c>
       <c r="O8" t="n">
-        <v>113200854750</v>
+        <v>3121538996250</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>85000</v>
+        <v>230000</v>
       </c>
       <c r="S8" t="n">
-        <v>2000</v>
+        <v>-235000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>뉴스케일파워와의 연관성 및 스페이스X 선택에 대한 언급이 있으며, 주주 환원 정책에 대한 요구가 있습니다. 일부에서는 긍정적인 주가 흐름을 기대합니다.</t>
+          <t>정치적 논쟁과 함께 일부 투자자들의 부정적인 전망 혼재. 외인 매도세 지속에 대한 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '주주환원', '원전']</t>
+          <t>['역배열', '외인 이탈', '피크 아웃']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>219000</v>
+        <v>42300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.29%</t>
+          <t>'+3.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.18</v>
+        <v>0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>289</v>
       </c>
       <c r="F9" t="n">
-        <v>489</v>
+        <v>138</v>
       </c>
       <c r="G9" t="n">
-        <v>1272</v>
+        <v>1191</v>
       </c>
       <c r="H9" t="n">
-        <v>45.98</v>
+        <v>12.97</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>210000</v>
+        <v>40750</v>
       </c>
       <c r="K9" t="n">
-        <v>215000</v>
+        <v>40600</v>
       </c>
       <c r="L9" t="n">
-        <v>222500</v>
+        <v>42500</v>
       </c>
       <c r="M9" t="n">
-        <v>210500</v>
+        <v>40050</v>
       </c>
       <c r="N9" t="n">
-        <v>46.16</v>
+        <v>12.84</v>
       </c>
       <c r="O9" t="n">
-        <v>3041413965250</v>
+        <v>16294158475</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>230000</v>
+        <v>73000</v>
       </c>
       <c r="S9" t="n">
-        <v>-235000</v>
+        <v>-8000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>직원 상여금 지급 반대 주장과 함께 정부 정책 및 외인 이탈에 대한 부정적 언급이 존재합니다. 일부에서는 상승 가능성을 제기합니다.</t>
+          <t>CLASS1 발표 및 FDA 승인에 대한 기대감이 높은 가운데, 과거 사례와 비교하며 신중론을 제기하는 의견도 있습니다. 야간 선물 급등에 대한 언급도 있습니다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이평선', '저항선', '외인']</t>
+          <t>['CLASS1', 'FDA승인', '담관암']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42350</v>
+        <v>65700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.93%</t>
+          <t>'+3.79%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.13</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>286</v>
+        <v>154</v>
       </c>
       <c r="F10" t="n">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="G10" t="n">
-        <v>1173</v>
+        <v>545</v>
       </c>
       <c r="H10" t="n">
-        <v>12.97</v>
+        <v>22.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>40750</v>
+        <v>63300</v>
       </c>
       <c r="K10" t="n">
-        <v>40600</v>
+        <v>63900</v>
       </c>
       <c r="L10" t="n">
-        <v>42500</v>
+        <v>66400</v>
       </c>
       <c r="M10" t="n">
-        <v>40050</v>
+        <v>63500</v>
       </c>
       <c r="N10" t="n">
-        <v>12.84</v>
+        <v>22.11</v>
       </c>
       <c r="O10" t="n">
-        <v>15952817975</v>
+        <v>116528466150</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>73000</v>
+        <v>85000</v>
       </c>
       <c r="S10" t="n">
-        <v>-8000</v>
+        <v>2000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>CLASS1 발표 및 FDA 승인에 대한 기대감이 높은 가운데, 과거 사례와 비교하며 신중론을 제기하는 의견도 있습니다. 야간 선물 급등에 대한 언급도 있습니다.</t>
+          <t>뉴스케일파워 등 관련 업종 상승 속에서 주가 반등 시도. 주주 환원 정책 요구 및 신뢰도 문제 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['CLASS1', 'FDA승인', '담관암']</t>
+          <t>['뉴스케일파워', '원전주', '주주 환원']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18810</v>
+        <v>18710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.52%</t>
+          <t>'+2.97%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H11" t="n">
         <v>27.77</v>
@@ -1438,7 +1438,7 @@
         <v>27.82</v>
       </c>
       <c r="O11" t="n">
-        <v>46658436260</v>
+        <v>48099716360</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13470</v>
+        <v>13440</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+2.91%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="H12" t="n">
         <v>3.42</v>
@@ -1530,7 +1530,7 @@
         <v>3.21</v>
       </c>
       <c r="O12" t="n">
-        <v>45563195580</v>
+        <v>45939959145</v>
       </c>
       <c r="P12" t="n">
         <v>31500</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1301000</v>
+        <v>1291000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.09%</t>
+          <t>'+2.30%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G13" t="n">
-        <v>1301</v>
+        <v>1247</v>
       </c>
       <c r="H13" t="n">
         <v>48.85</v>
@@ -1622,7 +1622,7 @@
         <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>4398767424000</v>
+        <v>4524852799500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1634,20 +1634,20 @@
         <v>-543000</v>
       </c>
       <c r="S13" t="n">
-        <v>-39000</v>
+        <v>-18000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 경영진 비판과 함께 정부 정책 및 외인 자금 이탈에 대한 부정적인 인식이 강하게 나타납니다. 솔리다임 관련 이슈도 언급됩니다.</t>
+          <t>경영진의 주가 관리 부재 및 솔리다임 이슈로 인한 주가 하락에 대한 불만 고조. 외국인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가관리', '외인', '솔리다임']</t>
+          <t>['솔리다임', '주가 하락', '외국인']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15040</v>
+        <v>14960</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.52%</t>
+          <t>'+1.98%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F14" t="n">
         <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="H14" t="n">
         <v>9.779999999999999</v>
@@ -1714,7 +1714,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>33714134060</v>
+        <v>34862380585</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대규모 공급 계약 체결 공시가 있었으며, 주가 조작 의혹 및 금융 당국의 사모펀드 점검에 대한 언급이 있습니다. 긍정적인 전망을 제시하는 의견도 존재합니다.</t>
+          <t>대규모 공급 계약 체결 공시. 주가 조작 관련 정치적 이슈와 함께 긍정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공급계약', '공시', '주가조작']</t>
+          <t>['공급 계약', '재개발 사업', '주가 조작']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23700</v>
+        <v>23650</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.16%</t>
+          <t>'+1.94%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="H15" t="n">
         <v>9.23</v>
@@ -1806,7 +1806,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>43909485750</v>
+        <v>44561635850</v>
       </c>
       <c r="P15" t="n">
         <v>24950</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17550</v>
+        <v>20450</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.46%</t>
+          <t>'-1.45%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E16" t="n">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="F16" t="n">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="G16" t="n">
-        <v>386</v>
+        <v>323</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17470</v>
+        <v>20750</v>
       </c>
       <c r="K16" t="n">
-        <v>18710</v>
+        <v>20500</v>
       </c>
       <c r="L16" t="n">
-        <v>20300</v>
+        <v>21550</v>
       </c>
       <c r="M16" t="n">
-        <v>17250</v>
+        <v>19440</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O16" t="n">
-        <v>163879307415</v>
+        <v>73350405895</v>
       </c>
       <c r="P16" t="n">
-        <v>28800</v>
+        <v>22450</v>
       </c>
       <c r="Q16" t="n">
-        <v>15780</v>
+        <v>6320</v>
       </c>
       <c r="R16" t="n">
-        <v>4000</v>
+        <v>-49000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 상승 및 하락에 대한 상반된 전망. 반도체 테마 내에서의 저평가 논의 및 수급 불안정성 언급.</t>
+          <t>양자보안 관련 신규 납품 및 해킹 시도 증가 뉴스. 긍정적 전망과 함께 외국인 매수세 주목.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['저평가', '수급', '반도체']</t>
+          <t>['양자보안', '납품', '해킹']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20650</v>
+        <v>16910</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.48%</t>
+          <t>'-3.21%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="F17" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="G17" t="n">
-        <v>313</v>
+        <v>414</v>
       </c>
       <c r="H17" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>20750</v>
+        <v>17470</v>
       </c>
       <c r="K17" t="n">
-        <v>20500</v>
+        <v>18710</v>
       </c>
       <c r="L17" t="n">
-        <v>21550</v>
+        <v>20300</v>
       </c>
       <c r="M17" t="n">
-        <v>19440</v>
+        <v>16800</v>
       </c>
       <c r="N17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>72574300845</v>
+        <v>168641207380</v>
       </c>
       <c r="P17" t="n">
-        <v>22450</v>
+        <v>28800</v>
       </c>
       <c r="Q17" t="n">
-        <v>6320</v>
+        <v>15780</v>
       </c>
       <c r="R17" t="n">
-        <v>-49000</v>
+        <v>4000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>농협, KDB 등으로부터 신규 납품 요청 및 러브콜이 쇄도한다는 뉴스와 함께 금융권 보안 투자 확대 소식이 있습니다. 양자보안 관련 긍정적 전망이 제시됩니다.</t>
+          <t>주가 상승 및 하락에 대한 상반된 전망. 반도체 테마 내에서의 저평가 논의 및 수급 불안정성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자보안', '보안투자', '납품요청']</t>
+          <t>['저평가', '수급', '반도체']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26775</v>
+        <v>26750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.08%</t>
+          <t>'-9.17%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="F18" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G18" t="n">
-        <v>675</v>
+        <v>716</v>
       </c>
       <c r="H18" t="n">
-        <v>53.3</v>
+        <v>53.26</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2076,13 +2076,13 @@
         <v>29600</v>
       </c>
       <c r="M18" t="n">
-        <v>26650</v>
+        <v>26600</v>
       </c>
       <c r="N18" t="n">
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>168232366575</v>
+        <v>174455755650</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 급락 및 외인/기관의 대규모 매도에 대한 불만과 하락 추세에 대한 경고가 주를 이룹니다. 신한 증권에 대한 비판도 나타납니다.</t>
+          <t>실적 발표 후 큰 폭의 하락세. 외인 매도 및 의도적인 주가 하락 우려 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적발표', '외인', '매도']</t>
+          <t>['실적 발표', '외인 매도', '유증']</t>
         </is>
       </c>
       <c r="X18" t="n">

--- a/data/trending_integrated_20261016_14.xlsx
+++ b/data/trending_integrated_20261016_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9080</v>
+        <v>8980</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+26.99%</t>
+          <t>'+25.59%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F2" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G2" t="n">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>235439017330</v>
+        <v>240931438155</v>
       </c>
       <c r="P2" t="n">
         <v>9180</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7930</v>
+        <v>7980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.70%</t>
+          <t>'+21.46%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>80687584105</v>
+        <v>81327146735</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8180</v>
+        <v>8230</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.41%</t>
+          <t>'+15.10%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>53978403205</v>
+        <v>54244562055</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -854,13 +854,13 @@
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>92452849540</v>
+        <v>92924695005</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -931,184 +931,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10390</v>
+        <v>15780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.63%</t>
+          <t>'+5.62%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>257</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>150</v>
+        <v>255</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9930</v>
+        <v>14940</v>
       </c>
       <c r="K6" t="n">
-        <v>10100</v>
+        <v>14940</v>
       </c>
       <c r="L6" t="n">
-        <v>11100</v>
+        <v>16350</v>
       </c>
       <c r="M6" t="n">
-        <v>9860</v>
+        <v>14330</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>33214724715</v>
+        <v>79187866895</v>
       </c>
       <c r="P6" t="n">
-        <v>19380</v>
+        <v>30800</v>
       </c>
       <c r="Q6" t="n">
-        <v>3200</v>
+        <v>9810</v>
       </c>
       <c r="R6" t="n">
-        <v>-128000</v>
+        <v>-2000</v>
       </c>
       <c r="S6" t="n">
-        <v>-10000</v>
+        <v>3000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>상장 사기 및 공모가 고평가 논란. 경영진 사퇴 요구와 함께 주가 부양 및 상폐 압박.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['상장 사기', '공모가 고평가', '경영진 사퇴']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15590</v>
+        <v>10360</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.35%</t>
+          <t>'+4.33%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>247</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>246</v>
+        <v>150</v>
       </c>
       <c r="H7" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14940</v>
+        <v>9930</v>
       </c>
       <c r="K7" t="n">
-        <v>14940</v>
+        <v>10100</v>
       </c>
       <c r="L7" t="n">
-        <v>16350</v>
+        <v>11100</v>
       </c>
       <c r="M7" t="n">
-        <v>14330</v>
+        <v>9860</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>73781750980</v>
+        <v>33411869615</v>
       </c>
       <c r="P7" t="n">
-        <v>30800</v>
+        <v>19380</v>
       </c>
       <c r="Q7" t="n">
-        <v>9810</v>
+        <v>3200</v>
       </c>
       <c r="R7" t="n">
-        <v>-2000</v>
+        <v>-128000</v>
       </c>
       <c r="S7" t="n">
-        <v>3000</v>
+        <v>-10000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>상장 사기 의혹과 경영진 사퇴 요구가 제기되며, 공모가 대비 높은 가격에 대한 비판이 있습니다. 회사에 직접 전화하자는 의견도 있습니다.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['상장사기', '공모가', '경영진']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>218500</v>
+        <v>217500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.05%</t>
+          <t>'+3.57%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="G8" t="n">
-        <v>1309</v>
+        <v>1344</v>
       </c>
       <c r="H8" t="n">
         <v>45.98</v>
@@ -1162,7 +1162,7 @@
         <v>46.16</v>
       </c>
       <c r="O8" t="n">
-        <v>3121538996250</v>
+        <v>3220769847750</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 논쟁과 함께 일부 투자자들의 부정적인 전망 혼재. 외인 매도세 지속에 대한 우려.</t>
+          <t>정치적 요인 및 노사 문제로 인한 외국인 이탈 및 주가 하락 우려. 일부 긍정적인 전망도 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['역배열', '외인 이탈', '피크 아웃']</t>
+          <t>['외국인 이탈', '정치적 요인', '주가 전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42300</v>
+        <v>65500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.80%</t>
+          <t>'+3.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.13</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>289</v>
+        <v>154</v>
       </c>
       <c r="F9" t="n">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
-        <v>1191</v>
+        <v>547</v>
       </c>
       <c r="H9" t="n">
-        <v>12.97</v>
+        <v>22.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>40750</v>
+        <v>63300</v>
       </c>
       <c r="K9" t="n">
-        <v>40600</v>
+        <v>63900</v>
       </c>
       <c r="L9" t="n">
-        <v>42500</v>
+        <v>66400</v>
       </c>
       <c r="M9" t="n">
-        <v>40050</v>
+        <v>63500</v>
       </c>
       <c r="N9" t="n">
-        <v>12.84</v>
+        <v>22.11</v>
       </c>
       <c r="O9" t="n">
-        <v>16294158475</v>
+        <v>120630920700</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>73000</v>
+        <v>85000</v>
       </c>
       <c r="S9" t="n">
-        <v>-8000</v>
+        <v>2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>CLASS1 발표 및 FDA 승인에 대한 기대감이 높은 가운데, 과거 사례와 비교하며 신중론을 제기하는 의견도 있습니다. 야간 선물 급등에 대한 언급도 있습니다.</t>
+          <t>원전 사업 및 스페이스X 관련 성장 기대감. 주주 환원 정책 부재 및 신뢰도 하락 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['CLASS1', 'FDA승인', '담관암']</t>
+          <t>['원전 사업', '뉴스케일파워', '주주 환원']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65700</v>
+        <v>42150</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.79%</t>
+          <t>'+3.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>154</v>
+        <v>290</v>
       </c>
       <c r="F10" t="n">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="G10" t="n">
-        <v>545</v>
+        <v>1216</v>
       </c>
       <c r="H10" t="n">
-        <v>22.1</v>
+        <v>12.97</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>63300</v>
+        <v>40750</v>
       </c>
       <c r="K10" t="n">
-        <v>63900</v>
+        <v>40600</v>
       </c>
       <c r="L10" t="n">
-        <v>66400</v>
+        <v>42500</v>
       </c>
       <c r="M10" t="n">
-        <v>63500</v>
+        <v>40050</v>
       </c>
       <c r="N10" t="n">
-        <v>22.11</v>
+        <v>12.84</v>
       </c>
       <c r="O10" t="n">
-        <v>116528466150</v>
+        <v>16931821550</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>85000</v>
+        <v>73000</v>
       </c>
       <c r="S10" t="n">
-        <v>2000</v>
+        <v>-8000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>뉴스케일파워 등 관련 업종 상승 속에서 주가 반등 시도. 주주 환원 정책 요구 및 신뢰도 문제 제기.</t>
+          <t>C1 발표 및 FDA 승인에 대한 기대감. 임상 결과 및 규제 관련 불확실성 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '원전주', '주주 환원']</t>
+          <t>['C1 발표', 'FDA 승인', '임상 결과']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18710</v>
+        <v>18720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.97%</t>
+          <t>'+3.03%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F11" t="n">
         <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H11" t="n">
         <v>27.77</v>
@@ -1438,7 +1438,7 @@
         <v>27.82</v>
       </c>
       <c r="O11" t="n">
-        <v>48099716360</v>
+        <v>49666914280</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13440</v>
+        <v>13450</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.91%</t>
+          <t>'+2.99%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H12" t="n">
         <v>3.42</v>
@@ -1530,7 +1530,7 @@
         <v>3.21</v>
       </c>
       <c r="O12" t="n">
-        <v>45939959145</v>
+        <v>46852963515</v>
       </c>
       <c r="P12" t="n">
         <v>31500</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1291000</v>
+        <v>23700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.30%</t>
+          <t>'+2.16%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.17</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>468</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>1247</v>
+        <v>459</v>
       </c>
       <c r="H13" t="n">
-        <v>48.85</v>
+        <v>9.23</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1262000</v>
+        <v>23200</v>
       </c>
       <c r="K13" t="n">
-        <v>1290000</v>
+        <v>23250</v>
       </c>
       <c r="L13" t="n">
-        <v>1325000</v>
+        <v>24250</v>
       </c>
       <c r="M13" t="n">
-        <v>1247000</v>
+        <v>22900</v>
       </c>
       <c r="N13" t="n">
-        <v>49.02</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>4524852799500</v>
+        <v>45189962575</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>24950</v>
       </c>
       <c r="Q13" t="n">
-        <v>420500</v>
+        <v>17910</v>
       </c>
       <c r="R13" t="n">
-        <v>-543000</v>
+        <v>635000</v>
       </c>
       <c r="S13" t="n">
-        <v>-18000</v>
+        <v>27000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>경영진의 주가 관리 부재 및 솔리다임 이슈로 인한 주가 하락에 대한 불만 고조. 외국인 매도세 관찰.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['솔리다임', '주가 하락', '외국인']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14960</v>
+        <v>14910</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.98%</t>
+          <t>'+1.64%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="H14" t="n">
         <v>9.779999999999999</v>
@@ -1714,7 +1714,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>34862380585</v>
+        <v>35997307100</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23650</v>
+        <v>1282000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.94%</t>
+          <t>'+1.58%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="E15" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>462</v>
       </c>
       <c r="G15" t="n">
-        <v>457</v>
+        <v>1049</v>
       </c>
       <c r="H15" t="n">
-        <v>9.23</v>
+        <v>48.85</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,60 +1791,60 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>23200</v>
+        <v>1262000</v>
       </c>
       <c r="K15" t="n">
-        <v>23250</v>
+        <v>1290000</v>
       </c>
       <c r="L15" t="n">
-        <v>24250</v>
+        <v>1325000</v>
       </c>
       <c r="M15" t="n">
-        <v>22900</v>
+        <v>1247000</v>
       </c>
       <c r="N15" t="n">
-        <v>9.210000000000001</v>
+        <v>49.02</v>
       </c>
       <c r="O15" t="n">
-        <v>44561635850</v>
+        <v>4699918981000</v>
       </c>
       <c r="P15" t="n">
-        <v>24950</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>17910</v>
+        <v>420500</v>
       </c>
       <c r="R15" t="n">
-        <v>635000</v>
+        <v>-543000</v>
       </c>
       <c r="S15" t="n">
-        <v>27000</v>
+        <v>-18000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>솔리다임 상장 철회 요구와 함께 주가 급락에 대한 책임 논란. 정부 정책 및 경영진 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['솔리다임', '주가 급락', '경영진 비판']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20450</v>
+        <v>20350</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-1.93%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2.5</v>
       </c>
       <c r="E16" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F16" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G16" t="n">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="H16" t="n">
         <v>4.28</v>
@@ -1898,7 +1898,7 @@
         <v>1.78</v>
       </c>
       <c r="O16" t="n">
-        <v>73350405895</v>
+        <v>73951244320</v>
       </c>
       <c r="P16" t="n">
         <v>22450</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>양자보안 관련 신규 납품 및 해킹 시도 증가 뉴스. 긍정적 전망과 함께 외국인 매수세 주목.</t>
+          <t>양자보안 관련 신규 납품 및 수주 기대감. 금융권 보안 강화 및 해킹 시도 증가로 인한 수혜 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자보안', '납품', '해킹']</t>
+          <t>['양자보안', '신규 납품', '보안 강화']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16910</v>
+        <v>16400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.21%</t>
+          <t>'-6.12%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="F17" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="G17" t="n">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1984,13 +1984,13 @@
         <v>20300</v>
       </c>
       <c r="M17" t="n">
-        <v>16800</v>
+        <v>15920</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>168641207380</v>
+        <v>178816698715</v>
       </c>
       <c r="P17" t="n">
         <v>28800</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 상승 및 하락에 대한 상반된 전망. 반도체 테마 내에서의 저평가 논의 및 수급 불안정성 언급.</t>
+          <t>종목 자체에 대한 정보 부족 및 관망세. 일부 매수 및 매도 타이밍에 대한 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['저평가', '수급', '반도체']</t>
+          <t>['반도체 테마', '시가총액', '매수/매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F18" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G18" t="n">
-        <v>716</v>
+        <v>738</v>
       </c>
       <c r="H18" t="n">
         <v>53.26</v>
@@ -2082,7 +2082,7 @@
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>174455755650</v>
+        <v>177554297050</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 큰 폭의 하락세. 외인 매도 및 의도적인 주가 하락 우려 제기.</t>
+          <t>실적 발표 후 급락, 외인 매도 및 유증 가능성 제기. 주가 하락에 대한 부정적 전망이 지배적.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적 발표', '외인 매도', '유증']</t>
+          <t>['실적 발표', '외인 매도', '유증 가능성']</t>
         </is>
       </c>
       <c r="X18" t="n">

--- a/data/trending_integrated_20261016_14.xlsx
+++ b/data/trending_integrated_20261016_14.xlsx
@@ -578,13 +578,13 @@
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G2" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>240931438155</v>
+        <v>245404948395</v>
       </c>
       <c r="P2" t="n">
         <v>9180</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>장기 보유 물량 일부 매도 관찰. 인수합병 기대감 및 2차전지 섹터 편입 가능성 언급.</t>
+          <t>상장 후 4년 묵은 물량 매집 및 상승 기대. 공매도 상환 및 텐버거 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '2차전지', '텐버거']</t>
+          <t>['인수합병', '공매도', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7980</v>
+        <v>8030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.46%</t>
+          <t>'+22.22%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
         <v>240</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>81327146735</v>
+        <v>81714566610</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군 공항 이전 관련 정치적 이슈와 함께 주가 급등 및 하락 혼재. 투경 종목으로 변동성 확대.</t>
+          <t>군공항 이전 및 호남 관련주 상승 기대. 투경, 급락 주의보 등 단기 변동성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군 공항 이전', '투경', '급등']</t>
+          <t>['군공항이전', '호남관련주', '투경']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8230</v>
+        <v>8480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.10%</t>
+          <t>'+18.60%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>54244562055</v>
+        <v>56638421440</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>92924695005</v>
+        <v>93436605000</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -931,123 +931,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15780</v>
+        <v>10370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.62%</t>
+          <t>'+4.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>257</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>255</v>
+        <v>150</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14940</v>
+        <v>9930</v>
       </c>
       <c r="K6" t="n">
-        <v>14940</v>
+        <v>10100</v>
       </c>
       <c r="L6" t="n">
-        <v>16350</v>
+        <v>11100</v>
       </c>
       <c r="M6" t="n">
-        <v>14330</v>
+        <v>9860</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>79187866895</v>
+        <v>33606507380</v>
       </c>
       <c r="P6" t="n">
-        <v>30800</v>
+        <v>19380</v>
       </c>
       <c r="Q6" t="n">
-        <v>9810</v>
+        <v>3200</v>
       </c>
       <c r="R6" t="n">
-        <v>-2000</v>
+        <v>-128000</v>
       </c>
       <c r="S6" t="n">
-        <v>3000</v>
+        <v>-10000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>상장 사기 및 공모가 고평가 논란. 경영진 사퇴 요구와 함께 주가 부양 및 상폐 압박.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['상장 사기', '공모가 고평가', '경영진 사퇴']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10360</v>
+        <v>218500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.33%</t>
+          <t>'+4.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>491</v>
       </c>
       <c r="G7" t="n">
-        <v>150</v>
+        <v>1329</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>45.98</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,130 +1055,130 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9930</v>
+        <v>210000</v>
       </c>
       <c r="K7" t="n">
-        <v>10100</v>
+        <v>215000</v>
       </c>
       <c r="L7" t="n">
-        <v>11100</v>
+        <v>222500</v>
       </c>
       <c r="M7" t="n">
-        <v>9860</v>
+        <v>210500</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>33411869615</v>
+        <v>3292997803250</v>
       </c>
       <c r="P7" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3200</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-128000</v>
+        <v>230000</v>
       </c>
       <c r="S7" t="n">
-        <v>-10000</v>
+        <v>-235000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>정치적 요인 및 노사 문제로 인한 외국인 이탈 및 주가 하락 우려. 일부 긍정적인 전망도 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['외국인 이탈', '정치적 요인', '주가 전망']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>217500</v>
+        <v>15510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.57%</t>
+          <t>'+3.82%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>271</v>
       </c>
       <c r="F8" t="n">
-        <v>491</v>
+        <v>98</v>
       </c>
       <c r="G8" t="n">
-        <v>1344</v>
+        <v>258</v>
       </c>
       <c r="H8" t="n">
-        <v>45.98</v>
+        <v>0.11</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>210000</v>
+        <v>14940</v>
       </c>
       <c r="K8" t="n">
-        <v>215000</v>
+        <v>14940</v>
       </c>
       <c r="L8" t="n">
-        <v>222500</v>
+        <v>16350</v>
       </c>
       <c r="M8" t="n">
-        <v>210500</v>
+        <v>14330</v>
       </c>
       <c r="N8" t="n">
-        <v>46.16</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3220769847750</v>
+        <v>80701460030</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>30800</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>9810</v>
       </c>
       <c r="R8" t="n">
-        <v>230000</v>
+        <v>-2000</v>
       </c>
       <c r="S8" t="n">
-        <v>-235000</v>
+        <v>3000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 요인 및 노사 문제로 인한 외국인 이탈 및 주가 하락 우려. 일부 긍정적인 전망도 존재.</t>
+          <t>상장 사기 및 피해 주장. 경영진 사퇴 요구. 공모가 대비 고평가 및 상장 떠넘기기 의혹.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외국인 이탈', '정치적 요인', '주가 전망']</t>
+          <t>['상장사기', '공모가', '경영진']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65500</v>
+        <v>65600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.48%</t>
+          <t>'+3.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F9" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G9" t="n">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="H9" t="n">
         <v>22.1</v>
@@ -1254,7 +1254,7 @@
         <v>22.11</v>
       </c>
       <c r="O9" t="n">
-        <v>120630920700</v>
+        <v>122430983100</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전 사업 및 스페이스X 관련 성장 기대감. 주주 환원 정책 부재 및 신뢰도 하락 우려.</t>
+          <t>뉴스케일파워 연계 상승 기대. 의무공개매수제도 청원 언급. 주주환원정책 요구.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전 사업', '뉴스케일파워', '주주 환원']</t>
+          <t>['뉴스케일파워', '공개매수', '주주환원']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42150</v>
+        <v>13480</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.44%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="E10" t="n">
-        <v>290</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>1216</v>
+        <v>271</v>
       </c>
       <c r="H10" t="n">
-        <v>12.97</v>
+        <v>3.42</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,222 +1331,222 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>40750</v>
+        <v>13060</v>
       </c>
       <c r="K10" t="n">
-        <v>40600</v>
+        <v>13390</v>
       </c>
       <c r="L10" t="n">
-        <v>42500</v>
+        <v>13620</v>
       </c>
       <c r="M10" t="n">
-        <v>40050</v>
+        <v>12910</v>
       </c>
       <c r="N10" t="n">
-        <v>12.84</v>
+        <v>3.21</v>
       </c>
       <c r="O10" t="n">
-        <v>16931821550</v>
+        <v>47349521555</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>1640</v>
       </c>
       <c r="R10" t="n">
-        <v>73000</v>
+        <v>-102000</v>
       </c>
       <c r="S10" t="n">
-        <v>-8000</v>
+        <v>-10000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>C1 발표 및 FDA 승인에 대한 기대감. 임상 결과 및 규제 관련 불확실성 존재.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['C1 발표', 'FDA 승인', '임상 결과']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18720</v>
+        <v>42050</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.03%</t>
+          <t>'+3.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.05</v>
+        <v>0.13</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>295</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="G11" t="n">
-        <v>186</v>
+        <v>1231</v>
       </c>
       <c r="H11" t="n">
-        <v>27.77</v>
+        <v>12.97</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18170</v>
+        <v>40750</v>
       </c>
       <c r="K11" t="n">
-        <v>18340</v>
+        <v>40600</v>
       </c>
       <c r="L11" t="n">
-        <v>18990</v>
+        <v>42500</v>
       </c>
       <c r="M11" t="n">
-        <v>18110</v>
+        <v>40050</v>
       </c>
       <c r="N11" t="n">
-        <v>27.82</v>
+        <v>12.84</v>
       </c>
       <c r="O11" t="n">
-        <v>49666914280</v>
+        <v>17365857400</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>17210</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>518000</v>
+        <v>73000</v>
       </c>
       <c r="S11" t="n">
-        <v>172000</v>
+        <v>-8000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>C1 발표 및 FDA 승인에 대한 기대감. 임상 결과 및 규제 관련 불확실성 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['C1 발표', 'FDA 승인', '임상 결과']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13450</v>
+        <v>18700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+2.92%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
         <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H12" t="n">
-        <v>3.42</v>
+        <v>27.77</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13060</v>
+        <v>18170</v>
       </c>
       <c r="K12" t="n">
-        <v>13390</v>
+        <v>18340</v>
       </c>
       <c r="L12" t="n">
-        <v>13620</v>
+        <v>18990</v>
       </c>
       <c r="M12" t="n">
-        <v>12910</v>
+        <v>18110</v>
       </c>
       <c r="N12" t="n">
-        <v>3.21</v>
+        <v>27.82</v>
       </c>
       <c r="O12" t="n">
-        <v>46852963515</v>
+        <v>50918290230</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>1640</v>
+        <v>17210</v>
       </c>
       <c r="R12" t="n">
-        <v>-102000</v>
+        <v>518000</v>
       </c>
       <c r="S12" t="n">
-        <v>-10000</v>
+        <v>172000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23700</v>
+        <v>23750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.16%</t>
+          <t>'+2.37%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F13" t="n">
         <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="H13" t="n">
         <v>9.23</v>
@@ -1622,7 +1622,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>45189962575</v>
+        <v>46220546350</v>
       </c>
       <c r="P13" t="n">
         <v>24950</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14910</v>
+        <v>1288000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.64%</t>
+          <t>'+2.06%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="E14" t="n">
-        <v>243</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>457</v>
       </c>
       <c r="G14" t="n">
-        <v>547</v>
+        <v>1059</v>
       </c>
       <c r="H14" t="n">
-        <v>9.779999999999999</v>
+        <v>48.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14670</v>
+        <v>1262000</v>
       </c>
       <c r="K14" t="n">
-        <v>14800</v>
+        <v>1290000</v>
       </c>
       <c r="L14" t="n">
-        <v>15270</v>
+        <v>1325000</v>
       </c>
       <c r="M14" t="n">
-        <v>14800</v>
+        <v>1247000</v>
       </c>
       <c r="N14" t="n">
-        <v>9.710000000000001</v>
+        <v>49.02</v>
       </c>
       <c r="O14" t="n">
-        <v>35997307100</v>
+        <v>4846571660000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>420500</v>
       </c>
       <c r="R14" t="n">
-        <v>-134000</v>
+        <v>-543000</v>
       </c>
       <c r="S14" t="n">
-        <v>-61000</v>
+        <v>-18000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대규모 공급 계약 체결 공시. 주가 조작 관련 정치적 이슈와 함께 긍정적 전망 혼재.</t>
+          <t>솔리다임 상장 철회 요구. 정부 정책 및 연기금 매도 의혹 제기. 주가 하락 지속.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공급 계약', '재개발 사업', '주가 조작']</t>
+          <t>['솔리다임', '정부정책', '연기금']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1282000</v>
+        <v>14900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.58%</t>
+          <t>'+1.57%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>255</v>
       </c>
       <c r="F15" t="n">
-        <v>462</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>1049</v>
+        <v>592</v>
       </c>
       <c r="H15" t="n">
-        <v>48.85</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,47 +1791,47 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1262000</v>
+        <v>14670</v>
       </c>
       <c r="K15" t="n">
-        <v>1290000</v>
+        <v>14800</v>
       </c>
       <c r="L15" t="n">
-        <v>1325000</v>
+        <v>15270</v>
       </c>
       <c r="M15" t="n">
-        <v>1247000</v>
+        <v>14800</v>
       </c>
       <c r="N15" t="n">
-        <v>49.02</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>4699918981000</v>
+        <v>36639850220</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>420500</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-543000</v>
+        <v>-134000</v>
       </c>
       <c r="S15" t="n">
-        <v>-18000</v>
+        <v>-61000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 요구와 함께 주가 급락에 대한 책임 논란. 정부 정책 및 경영진 비판.</t>
+          <t>1.43조원 규모 공급계약 체결 공시. 건설주 상승 전망 및 대차해지 독려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['솔리다임', '주가 급락', '경영진 비판']</t>
+          <t>['공급계약', '재개발사업', '대차해지']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20350</v>
+        <v>20400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.93%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2.5</v>
       </c>
       <c r="E16" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F16" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G16" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H16" t="n">
         <v>4.28</v>
@@ -1898,7 +1898,7 @@
         <v>1.78</v>
       </c>
       <c r="O16" t="n">
-        <v>73951244320</v>
+        <v>74333006595</v>
       </c>
       <c r="P16" t="n">
         <v>22450</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16400</v>
+        <v>15970</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.12%</t>
+          <t>'-8.59%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="F17" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="G17" t="n">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1984,13 +1984,13 @@
         <v>20300</v>
       </c>
       <c r="M17" t="n">
-        <v>15920</v>
+        <v>15850</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>178816698715</v>
+        <v>183259804200</v>
       </c>
       <c r="P17" t="n">
         <v>28800</v>
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26750</v>
+        <v>26600</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.17%</t>
+          <t>'-9.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="F18" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G18" t="n">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="H18" t="n">
-        <v>53.26</v>
+        <v>53.21</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2076,13 +2076,13 @@
         <v>29600</v>
       </c>
       <c r="M18" t="n">
-        <v>26600</v>
+        <v>26550</v>
       </c>
       <c r="N18" t="n">
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>177554297050</v>
+        <v>186047769050</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 급락, 외인 매도 및 유증 가능성 제기. 주가 하락에 대한 부정적 전망이 지배적.</t>
+          <t>외인 매도세 및 급락 지속, 유증 가능성 제기. 종가 소량 매수 의견.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적 발표', '외인 매도', '유증 가능성']</t>
+          <t>['실적발표', '외인매도', '유증']</t>
         </is>
       </c>
       <c r="X18" t="n">
